--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
@@ -39,19 +39,22 @@
     <t xml:space="preserve">Lago Ranco</t>
   </si>
   <si>
+    <t xml:space="preserve">Futrono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panguipulli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paillaco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mariquina</t>
   </si>
   <si>
-    <t xml:space="preserve">Panguipulli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futrono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Lagos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paillaco</t>
+    <t xml:space="preserve">Máfil</t>
   </si>
   <si>
     <t xml:space="preserve">Lanco</t>
@@ -60,15 +63,12 @@
     <t xml:space="preserve">La Unión</t>
   </si>
   <si>
+    <t xml:space="preserve">Corral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Valdivia</t>
   </si>
   <si>
-    <t xml:space="preserve">Máfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Río Bueno</t>
   </si>
   <si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,7 +517,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.33</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="3">
@@ -528,13 +528,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14106</v>
+        <v>14202</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7.94</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="4">
@@ -545,13 +545,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>14108</v>
+        <v>14104</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7.25</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="5">
@@ -562,13 +562,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>14202</v>
+        <v>14108</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7.02</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="6">
@@ -579,13 +579,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>14104</v>
+        <v>14107</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.12</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>14107</v>
+        <v>14106</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5.09</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="8">
@@ -613,13 +613,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>14103</v>
+        <v>14105</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.96</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="9">
@@ -630,13 +630,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>14201</v>
+        <v>14103</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="10">
@@ -647,13 +647,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>14101</v>
+        <v>14201</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2.96</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="11">
@@ -664,13 +664,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>14105</v>
+        <v>14102</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.43</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>14102</v>
+        <v>14101</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.28</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-10.99</v>
+        <v>-1.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,7 +517,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.65</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="3">
@@ -534,7 +534,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.27</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="4">
@@ -551,7 +551,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.14</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="5">
@@ -568,7 +568,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.44</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.33</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="7">
@@ -602,7 +602,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.24</v>
+        <v>32.37</v>
       </c>
     </row>
     <row r="8">
@@ -619,7 +619,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.18</v>
+        <v>31.81</v>
       </c>
     </row>
     <row r="9">
@@ -636,7 +636,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.99</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="10">
@@ -653,7 +653,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.99</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.95</v>
+        <v>9.53</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +687,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.85</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-1.09</v>
+        <v>-10.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:33</t>
+    <t xml:space="preserve">2026-10-05 08:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
